--- a/Result/profitability/4108.xlsx
+++ b/Result/profitability/4108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.10875</v>
+        <v>-0.105</v>
       </c>
       <c r="N2" t="n">
-        <v>29.9575</v>
+        <v>29.7775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.14625</v>
+        <v>-0.13875</v>
       </c>
       <c r="N3" t="n">
-        <v>26.09375</v>
+        <v>24.6425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.17</v>
+        <v>-0.165</v>
       </c>
       <c r="N4" t="n">
-        <v>21.83125</v>
+        <v>22.51375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.20125</v>
+        <v>-0.19125</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6875</v>
+        <v>20.485</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.235</v>
+        <v>-0.23625</v>
       </c>
       <c r="N6" t="n">
-        <v>18.055</v>
+        <v>17.8525</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.30375</v>
+        <v>-0.29625</v>
       </c>
       <c r="N7" t="n">
-        <v>14.585</v>
+        <v>17.01375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4075</v>
+        <v>-0.40125</v>
       </c>
       <c r="N8" t="n">
-        <v>13.78875</v>
+        <v>14.08125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>-0.24</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.46625</v>
+        <v>-0.4662500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>11.79375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>36</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-108.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.06875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.3325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.340000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06617647058823528</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7272727272727273</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.380000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2037037037037037</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
